--- a/data/dividends_info_20260326.xlsx
+++ b/data/dividends_info_20260326.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50.95000076293945</v>
+        <v>51.45000076293945</v>
       </c>
       <c r="I2" t="n">
-        <v>1.373895955874398</v>
+        <v>1.360544197511898</v>
       </c>
       <c r="J2" t="n">
         <v>333</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.985999941825867</v>
+        <v>1.983999967575073</v>
       </c>
       <c r="I3" t="n">
-        <v>3.877140093428633</v>
+        <v>3.88104845052556</v>
       </c>
       <c r="J3" t="n">
         <v>242</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5.409999847412109</v>
+        <v>5.380000114440918</v>
       </c>
       <c r="I4" t="n">
-        <v>3.696857775248748</v>
+        <v>3.71747203988273</v>
       </c>
       <c r="J4" t="n">
         <v>235</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9.295000076293945</v>
+        <v>9.208999633789062</v>
       </c>
       <c r="I5" t="n">
-        <v>2.797202774243181</v>
+        <v>2.823325120418345</v>
       </c>
       <c r="J5" t="n">
         <v>116</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4.795000076293945</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="I7" t="n">
-        <v>2.502606842349583</v>
+        <v>2.362204759886205</v>
       </c>
       <c r="J7" t="n">
         <v>109</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>30.14999961853027</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.4975124441056695</v>
       </c>
       <c r="J9" t="n">
         <v>102</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>22.29999923706055</v>
+        <v>21.97999954223633</v>
       </c>
       <c r="I10" t="n">
-        <v>1.121076271538714</v>
+        <v>1.137397657900789</v>
       </c>
       <c r="J10" t="n">
         <v>88</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>21.45000076293945</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9090908767561168</v>
+        <v>0.8904109744139194</v>
       </c>
       <c r="J11" t="n">
         <v>88</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.139999866485596</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="I12" t="n">
-        <v>5.642023492858249</v>
+        <v>5.664062626601665</v>
       </c>
       <c r="J12" t="n">
         <v>88</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3.95199990272522</v>
+        <v>3.944000005722046</v>
       </c>
       <c r="I13" t="n">
-        <v>4.0485830956035</v>
+        <v>4.056795125960151</v>
       </c>
       <c r="J13" t="n">
         <v>88</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2.441999912261963</v>
+        <v>2.434000015258789</v>
       </c>
       <c r="I14" t="n">
-        <v>5.675675879595684</v>
+        <v>5.69433028476229</v>
       </c>
       <c r="J14" t="n">
         <v>88</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>59.02000045776367</v>
+        <v>58.58000183105469</v>
       </c>
       <c r="I15" t="n">
-        <v>1.06743475959619</v>
+        <v>1.075452339207715</v>
       </c>
       <c r="J15" t="n">
         <v>88</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>16.54999923706055</v>
+        <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>4.712991153820356</v>
+        <v>4.588235294117647</v>
       </c>
       <c r="J16" t="n">
         <v>88</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>20.07999992370605</v>
+        <v>19.78000068664551</v>
       </c>
       <c r="I17" t="n">
-        <v>4.233067745167203</v>
+        <v>4.297269820490342</v>
       </c>
       <c r="J17" t="n">
         <v>88</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6.349999904632568</v>
+        <v>6.326000213623047</v>
       </c>
       <c r="I18" t="n">
-        <v>2.855118153115793</v>
+        <v>2.865949950642908</v>
       </c>
       <c r="J18" t="n">
         <v>88</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7.739999771118164</v>
+        <v>7.78000020980835</v>
       </c>
       <c r="I19" t="n">
-        <v>3.359173225950095</v>
+        <v>3.341902223501415</v>
       </c>
       <c r="J19" t="n">
         <v>88</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>25.70000076293945</v>
+        <v>25.45000076293945</v>
       </c>
       <c r="I20" t="n">
-        <v>4.319066019642573</v>
+        <v>4.361492993023377</v>
       </c>
       <c r="J20" t="n">
         <v>70</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.8379999995231628</v>
+        <v>0.828000009059906</v>
       </c>
       <c r="I21" t="n">
-        <v>3.57995226934016</v>
+        <v>3.623188366152481</v>
       </c>
       <c r="J21" t="n">
         <v>67</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.549999952316284</v>
+        <v>2.509999990463257</v>
       </c>
       <c r="I23" t="n">
-        <v>7.058823661408212</v>
+        <v>7.171314768283262</v>
       </c>
       <c r="J23" t="n">
         <v>60</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>12.22000026702881</v>
+        <v>12.1899995803833</v>
       </c>
       <c r="I24" t="n">
-        <v>2.045826469206661</v>
+        <v>2.050861432368802</v>
       </c>
       <c r="J24" t="n">
         <v>60</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13.60000038146973</v>
+        <v>13.35000038146973</v>
       </c>
       <c r="I26" t="n">
-        <v>4.264705762731166</v>
+        <v>4.344569164245573</v>
       </c>
       <c r="J26" t="n">
         <v>60</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2.377000093460083</v>
+        <v>2.371999979019165</v>
       </c>
       <c r="I27" t="n">
-        <v>4.375262764445763</v>
+        <v>4.384485704886243</v>
       </c>
       <c r="J27" t="n">
         <v>53</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>8.887999534606934</v>
+        <v>8.996000289916992</v>
       </c>
       <c r="I28" t="n">
-        <v>3.262826453476238</v>
+        <v>3.223654853869239</v>
       </c>
       <c r="J28" t="n">
         <v>53</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.985999941825867</v>
+        <v>1.983999967575073</v>
       </c>
       <c r="I29" t="n">
-        <v>3.877140093428633</v>
+        <v>3.88104845052556</v>
       </c>
       <c r="J29" t="n">
         <v>53</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>33.83000183105469</v>
+        <v>33.75</v>
       </c>
       <c r="I30" t="n">
-        <v>4.847767990643562</v>
+        <v>4.859259259259259</v>
       </c>
       <c r="J30" t="n">
         <v>53</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>32.93999862670898</v>
+        <v>32.40999984741211</v>
       </c>
       <c r="I31" t="n">
-        <v>6.071645669038751</v>
+        <v>6.170934925689909</v>
       </c>
       <c r="J31" t="n">
         <v>53</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3.769999980926514</v>
+        <v>3.684000015258789</v>
       </c>
       <c r="I32" t="n">
-        <v>2.652519907319046</v>
+        <v>2.714440813947047</v>
       </c>
       <c r="J32" t="n">
         <v>53</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>34.79999923706055</v>
+        <v>34.40000152587891</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4266092047550861</v>
+        <v>0.4315697482987449</v>
       </c>
       <c r="J33" t="n">
         <v>53</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.42000007629395</v>
+        <v>22.15999984741211</v>
       </c>
       <c r="I34" t="n">
-        <v>4.103479022610588</v>
+        <v>4.151624577323449</v>
       </c>
       <c r="J34" t="n">
         <v>53</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8.100000381469727</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="I35" t="n">
-        <v>3.703703529277682</v>
+        <v>3.712871322186832</v>
       </c>
       <c r="J35" t="n">
         <v>53</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>73.30000305175781</v>
+        <v>73.13999938964844</v>
       </c>
       <c r="I36" t="n">
-        <v>1.418826680355861</v>
+        <v>1.421930556027858</v>
       </c>
       <c r="J36" t="n">
         <v>53</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>50.95000076293945</v>
+        <v>51.45000076293945</v>
       </c>
       <c r="I37" t="n">
-        <v>4.317958718462394</v>
+        <v>4.275996049323108</v>
       </c>
       <c r="J37" t="n">
         <v>53</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>7.585999965667725</v>
+        <v>7.491000175476074</v>
       </c>
       <c r="I38" t="n">
-        <v>11.33667286965644</v>
+        <v>11.48044292957642</v>
       </c>
       <c r="J38" t="n">
         <v>53</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>11.14999961853027</v>
+        <v>11.04500007629395</v>
       </c>
       <c r="I39" t="n">
-        <v>5.022421696493439</v>
+        <v>5.070167461582338</v>
       </c>
       <c r="J39" t="n">
         <v>53</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.769999980926514</v>
+        <v>1.75</v>
       </c>
       <c r="I40" t="n">
-        <v>2.259887030002217</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="J40" t="n">
         <v>53</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>8.859999656677246</v>
+        <v>8.680000305175781</v>
       </c>
       <c r="I41" t="n">
-        <v>3.386004645879507</v>
+        <v>3.456221076641133</v>
       </c>
       <c r="J41" t="n">
         <v>53</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.259999990463257</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I42" t="n">
-        <v>4.778761082112308</v>
+        <v>4.821428550901461</v>
       </c>
       <c r="J42" t="n">
         <v>53</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>62</v>
+        <v>64.30000305175781</v>
       </c>
       <c r="I43" t="n">
-        <v>3.32258064516129</v>
+        <v>3.203732351834911</v>
       </c>
       <c r="J43" t="n">
         <v>53</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>14.5</v>
+        <v>14.27999973297119</v>
       </c>
       <c r="I44" t="n">
-        <v>5.172413793103448</v>
+        <v>5.252100938547777</v>
       </c>
       <c r="J44" t="n">
         <v>53</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>15.34000015258789</v>
+        <v>15.42000007629395</v>
       </c>
       <c r="I45" t="n">
-        <v>1.955671427743691</v>
+        <v>1.945525282202866</v>
       </c>
       <c r="J45" t="n">
         <v>53</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>40.29999923706055</v>
+        <v>41.59999847412109</v>
       </c>
       <c r="I46" t="n">
-        <v>2.109181181369169</v>
+        <v>2.043269305715902</v>
       </c>
       <c r="J46" t="n">
         <v>53</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>29.92000007629395</v>
+        <v>29.42000007629395</v>
       </c>
       <c r="I47" t="n">
-        <v>2.840909083664968</v>
+        <v>2.88919101902013</v>
       </c>
       <c r="J47" t="n">
         <v>53</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>59.91999816894531</v>
+        <v>59.22000122070312</v>
       </c>
       <c r="I48" t="n">
-        <v>2.169559478848165</v>
+        <v>2.195204277614105</v>
       </c>
       <c r="J48" t="n">
         <v>53</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5.409999847412109</v>
+        <v>5.380000114440918</v>
       </c>
       <c r="I49" t="n">
-        <v>3.696857775248748</v>
+        <v>3.71747203988273</v>
       </c>
       <c r="J49" t="n">
         <v>53</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>21.29999923706055</v>
+        <v>21.60000038146973</v>
       </c>
       <c r="I50" t="n">
-        <v>4.694835848914343</v>
+        <v>4.629629547867429</v>
       </c>
       <c r="J50" t="n">
         <v>53</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>9.079999923706055</v>
+        <v>9.380000114440918</v>
       </c>
       <c r="I52" t="n">
-        <v>2.643171828376432</v>
+        <v>2.558635363239597</v>
       </c>
       <c r="J52" t="n">
         <v>53</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>19.125</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="I53" t="n">
-        <v>4.130718954248366</v>
+        <v>4.199893792822184</v>
       </c>
       <c r="J53" t="n">
         <v>53</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>4.454999923706055</v>
+        <v>4.505000114440918</v>
       </c>
       <c r="I54" t="n">
-        <v>2.087542123292216</v>
+        <v>2.064372866537464</v>
       </c>
       <c r="J54" t="n">
         <v>53</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>33.40000152587891</v>
+        <v>33</v>
       </c>
       <c r="I55" t="n">
-        <v>1.047904143743269</v>
+        <v>1.060606060606061</v>
       </c>
       <c r="J55" t="n">
         <v>53</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1.970000028610229</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="I56" t="n">
-        <v>3.045685234955455</v>
+        <v>3.061224430216099</v>
       </c>
       <c r="J56" t="n">
         <v>53</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>11.85000038146973</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="I57" t="n">
-        <v>1.687763658748461</v>
+        <v>1.694915226840727</v>
       </c>
       <c r="J57" t="n">
         <v>53</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>5.730000019073486</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I58" t="n">
-        <v>1.797556713039149</v>
+        <v>1.819788034925374</v>
       </c>
       <c r="J58" t="n">
         <v>53</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>5.166999816894531</v>
+        <v>5.073999881744385</v>
       </c>
       <c r="I59" t="n">
-        <v>3.677182247592835</v>
+        <v>3.744580300121727</v>
       </c>
       <c r="J59" t="n">
         <v>53</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>9.954999923706055</v>
+        <v>9.835000038146973</v>
       </c>
       <c r="I60" t="n">
-        <v>4.339527908697107</v>
+        <v>4.392475834513507</v>
       </c>
       <c r="J60" t="n">
         <v>53</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>25.89999961853027</v>
+        <v>25.57999992370605</v>
       </c>
       <c r="I61" t="n">
-        <v>1.698841723863193</v>
+        <v>1.72009382842974</v>
       </c>
       <c r="J61" t="n">
         <v>53</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>7.119999885559082</v>
+        <v>7.269999980926514</v>
       </c>
       <c r="I62" t="n">
-        <v>6.601123701606553</v>
+        <v>6.464924363591286</v>
       </c>
       <c r="J62" t="n">
         <v>53</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>52.11999893188477</v>
+        <v>51.45999908447266</v>
       </c>
       <c r="I63" t="n">
-        <v>2.686109034326055</v>
+        <v>2.720559706388395</v>
       </c>
       <c r="J63" t="n">
         <v>53</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>3.055000066757202</v>
+        <v>3.045000076293945</v>
       </c>
       <c r="I64" t="n">
-        <v>9.819967052191972</v>
+        <v>9.852216501916431</v>
       </c>
       <c r="J64" t="n">
         <v>53</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>3.509999990463257</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="I65" t="n">
-        <v>4.843304856464204</v>
+        <v>4.970760123029561</v>
       </c>
       <c r="J65" t="n">
         <v>53</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>3.089999914169312</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="I66" t="n">
-        <v>1.132686115604929</v>
+        <v>1.155115522458126</v>
       </c>
       <c r="J66" t="n">
         <v>53</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>5.829999923706055</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I67" t="n">
-        <v>5.660377432564756</v>
+        <v>5.631399189100186</v>
       </c>
       <c r="J67" t="n">
         <v>53</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.9340000152587891</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="I68" t="n">
-        <v>7.494646558501896</v>
+        <v>7.526881662541449</v>
       </c>
       <c r="J68" t="n">
         <v>53</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>46.27999877929688</v>
+        <v>48.47999954223633</v>
       </c>
       <c r="I69" t="n">
-        <v>1.534140057751287</v>
+        <v>1.464521465973695</v>
       </c>
       <c r="J69" t="n">
         <v>53</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>78.69999694824219</v>
+        <v>78.15000152587891</v>
       </c>
       <c r="I70" t="n">
-        <v>1.715374907686262</v>
+        <v>1.727447183162185</v>
       </c>
       <c r="J70" t="n">
         <v>53</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>3.604000091552734</v>
+        <v>3.812999963760376</v>
       </c>
       <c r="I71" t="n">
-        <v>4.716981012249581</v>
+        <v>4.45843172346496</v>
       </c>
       <c r="J71" t="n">
         <v>53</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>4.760000228881836</v>
+        <v>4.920000076293945</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8403360940467085</v>
+        <v>0.8130081174740657</v>
       </c>
       <c r="J72" t="n">
         <v>53</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>30.95000076293945</v>
+        <v>30.35000038146973</v>
       </c>
       <c r="I73" t="n">
-        <v>3.392568575498404</v>
+        <v>3.459637518294993</v>
       </c>
       <c r="J73" t="n">
         <v>53</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>17.36000061035156</v>
+        <v>17.04999923706055</v>
       </c>
       <c r="I74" t="n">
-        <v>2.188940015206051</v>
+        <v>2.228739102662346</v>
       </c>
       <c r="J74" t="n">
         <v>53</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>24.71999931335449</v>
+        <v>25.36000061035156</v>
       </c>
       <c r="I75" t="n">
-        <v>2.427184533439132</v>
+        <v>2.365930542427074</v>
       </c>
       <c r="J75" t="n">
         <v>53</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>28.54999923706055</v>
+        <v>28.79999923706055</v>
       </c>
       <c r="I76" t="n">
-        <v>1.225919472339837</v>
+        <v>1.215277809971645</v>
       </c>
       <c r="J76" t="n">
         <v>53</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2.348000049591064</v>
+        <v>2.308000087738037</v>
       </c>
       <c r="I77" t="n">
-        <v>3.449744390512566</v>
+        <v>3.509531928977711</v>
       </c>
       <c r="J77" t="n">
         <v>53</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>9.300000190734863</v>
+        <v>9.420000076293945</v>
       </c>
       <c r="I78" t="n">
-        <v>3.763440783030176</v>
+        <v>3.715498908336511</v>
       </c>
       <c r="J78" t="n">
         <v>46</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>4.760000228881836</v>
+        <v>4.579999923706055</v>
       </c>
       <c r="I79" t="n">
-        <v>2.0168066257121</v>
+        <v>2.096069903912105</v>
       </c>
       <c r="J79" t="n">
         <v>46</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>14.46000003814697</v>
+        <v>14.30000019073486</v>
       </c>
       <c r="I80" t="n">
-        <v>3.457814652012091</v>
+        <v>3.496503449866776</v>
       </c>
       <c r="J80" t="n">
         <v>46</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>6.909999847412109</v>
+        <v>6.980000019073486</v>
       </c>
       <c r="I82" t="n">
-        <v>3.183791676672656</v>
+        <v>3.15186245557063</v>
       </c>
       <c r="J82" t="n">
         <v>46</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>3.460000038146973</v>
+        <v>3.424999952316284</v>
       </c>
       <c r="I83" t="n">
-        <v>4.624277405664109</v>
+        <v>4.671532911753591</v>
       </c>
       <c r="J83" t="n">
         <v>39</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>19.04000091552734</v>
+        <v>18.92000007629395</v>
       </c>
       <c r="I84" t="n">
-        <v>3.203781358553075</v>
+        <v>3.224101466914407</v>
       </c>
       <c r="J84" t="n">
         <v>39</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>12.05000019073486</v>
+        <v>11.94999980926514</v>
       </c>
       <c r="I85" t="n">
-        <v>5.809128538754909</v>
+        <v>5.857740679269905</v>
       </c>
       <c r="J85" t="n">
         <v>39</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>8.680000305175781</v>
+        <v>8.569999694824219</v>
       </c>
       <c r="I86" t="n">
-        <v>5.881336198750994</v>
+        <v>5.956826349810867</v>
       </c>
       <c r="J86" t="n">
         <v>39</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>7.400000095367432</v>
+        <v>7.644999980926514</v>
       </c>
       <c r="I87" t="n">
-        <v>3.648648601626724</v>
+        <v>3.531720087293946</v>
       </c>
       <c r="J87" t="n">
         <v>39</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>5.059999942779541</v>
+        <v>4.945000171661377</v>
       </c>
       <c r="I88" t="n">
-        <v>6.916996125650927</v>
+        <v>7.07785617492527</v>
       </c>
       <c r="J88" t="n">
         <v>39</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>18.60000038146973</v>
+        <v>18.20000076293945</v>
       </c>
       <c r="I90" t="n">
-        <v>4.032257981818046</v>
+        <v>4.120878948132905</v>
       </c>
       <c r="J90" t="n">
         <v>39</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>10.10000038146973</v>
+        <v>10</v>
       </c>
       <c r="I91" t="n">
-        <v>4.257425581774359</v>
+        <v>4.3</v>
       </c>
       <c r="J91" t="n">
         <v>39</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>3.960000038146973</v>
+        <v>3.845000028610229</v>
       </c>
       <c r="I92" t="n">
-        <v>3.787878751389872</v>
+        <v>3.901170322077145</v>
       </c>
       <c r="J92" t="n">
         <v>39</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>12.02000045776367</v>
+        <v>12.22000026702881</v>
       </c>
       <c r="I93" t="n">
-        <v>1.640341035699789</v>
+        <v>1.613494236428032</v>
       </c>
       <c r="J93" t="n">
         <v>39</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>26.35000038146973</v>
+        <v>26.54999923706055</v>
       </c>
       <c r="I94" t="n">
-        <v>4.174572994593047</v>
+        <v>4.143126296081149</v>
       </c>
       <c r="J94" t="n">
         <v>39</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>37.75</v>
+        <v>38.20000076293945</v>
       </c>
       <c r="I95" t="n">
-        <v>1.245033112582781</v>
+        <v>1.230366467573426</v>
       </c>
       <c r="J95" t="n">
         <v>39</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>2.349999904632568</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="I96" t="n">
-        <v>4.680851253787558</v>
+        <v>4.621848517256896</v>
       </c>
       <c r="J96" t="n">
         <v>39</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>75.90000152587891</v>
+        <v>75.80000305175781</v>
       </c>
       <c r="I97" t="n">
-        <v>1.581027636199516</v>
+        <v>1.583113392727194</v>
       </c>
       <c r="J97" t="n">
         <v>39</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>22.5</v>
+        <v>22.39999961853027</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>1.205357163384253</v>
       </c>
       <c r="J98" t="n">
         <v>39</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>10.30000019073486</v>
+        <v>10.19999980926514</v>
       </c>
       <c r="I99" t="n">
-        <v>3.689320320030873</v>
+        <v>3.725490265743223</v>
       </c>
       <c r="J99" t="n">
         <v>39</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>26.70000076293945</v>
+        <v>26.5</v>
       </c>
       <c r="I100" t="n">
-        <v>1.123595473511786</v>
+        <v>1.132075471698113</v>
       </c>
       <c r="J100" t="n">
         <v>39</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.1550000011920929</v>
+        <v>0.1509999930858612</v>
       </c>
       <c r="I101" t="n">
-        <v>4.516128997524869</v>
+        <v>4.635761801670864</v>
       </c>
       <c r="J101" t="n">
         <v>32</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>6.539999961853027</v>
+        <v>6.190000057220459</v>
       </c>
       <c r="I102" t="n">
-        <v>2.446483194698154</v>
+        <v>2.584814192584127</v>
       </c>
       <c r="J102" t="n">
         <v>32</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>2.174999952316284</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I103" t="n">
-        <v>2.988505812645086</v>
+        <v>2.954545390507408</v>
       </c>
       <c r="J103" t="n">
         <v>32</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>7.550000190734863</v>
+        <v>7.28000020980835</v>
       </c>
       <c r="I104" t="n">
-        <v>3.311258194493725</v>
+        <v>3.434065835096747</v>
       </c>
       <c r="J104" t="n">
         <v>32</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1.330000042915344</v>
+        <v>1.299999952316284</v>
       </c>
       <c r="I105" t="n">
-        <v>5.263157724909606</v>
+        <v>5.384615582121908</v>
       </c>
       <c r="J105" t="n">
         <v>32</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>17.07999992370605</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="I107" t="n">
-        <v>3.805620625898467</v>
+        <v>3.852993287874295</v>
       </c>
       <c r="J107" t="n">
         <v>25</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>12.00500011444092</v>
+        <v>11.90999984741211</v>
       </c>
       <c r="I108" t="n">
-        <v>4.498125738045012</v>
+        <v>4.534005095871896</v>
       </c>
       <c r="J108" t="n">
         <v>25</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>6.105999946594238</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="I109" t="n">
-        <v>1.63773339133056</v>
+        <v>1.633986958659309</v>
       </c>
       <c r="J109" t="n">
         <v>25</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>8.340000152587891</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I110" t="n">
-        <v>1.918465192717679</v>
+        <v>1.95121955758117</v>
       </c>
       <c r="J110" t="n">
         <v>25</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>276.3999938964844</v>
+        <v>279.7000122070312</v>
       </c>
       <c r="I111" t="n">
-        <v>1.307887148996779</v>
+        <v>1.292456146667671</v>
       </c>
       <c r="J111" t="n">
         <v>25</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>26.70000076293945</v>
+        <v>26.29999923706055</v>
       </c>
       <c r="I112" t="n">
-        <v>5.09363281325343</v>
+        <v>5.171102811606022</v>
       </c>
       <c r="J112" t="n">
         <v>25</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>13.42000007629395</v>
+        <v>13.19999980926514</v>
       </c>
       <c r="I113" t="n">
-        <v>4.359165399956935</v>
+        <v>4.43181824585623</v>
       </c>
       <c r="J113" t="n">
         <v>25</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>16.84000015258789</v>
+        <v>16.67499923706055</v>
       </c>
       <c r="I114" t="n">
-        <v>3.741092602681388</v>
+        <v>3.778111117389507</v>
       </c>
       <c r="J114" t="n">
         <v>25</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>98.41999816894531</v>
+        <v>95.87999725341797</v>
       </c>
       <c r="I115" t="n">
-        <v>0.914448299882187</v>
+        <v>0.9386733685663685</v>
       </c>
       <c r="J115" t="n">
         <v>25</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>62.40999984741211</v>
+        <v>61.15999984741211</v>
       </c>
       <c r="I116" t="n">
-        <v>2.75725044737579</v>
+        <v>2.813603669544177</v>
       </c>
       <c r="J116" t="n">
         <v>25</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>23.89999961853027</v>
+        <v>23.5</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5857740679269906</v>
+        <v>0.5957446808510638</v>
       </c>
       <c r="J117" t="n">
         <v>18</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1.980000019073486</v>
+        <v>1.950000047683716</v>
       </c>
       <c r="I119" t="n">
-        <v>1.717171700630076</v>
+        <v>1.743589700953418</v>
       </c>
       <c r="J119" t="n">
         <v>4</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>23.18000030517578</v>
+        <v>23.63999938964844</v>
       </c>
       <c r="I120" t="n">
-        <v>1.121656585750543</v>
+        <v>1.099830823658353</v>
       </c>
       <c r="J120" t="n">
         <v>-3</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>28.7450008392334</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="I121" t="n">
-        <v>0.31309792093365</v>
+        <v>0.3071672434931744</v>
       </c>
       <c r="J121" t="n">
         <v>-3</v>
@@ -7403,7 +7403,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7420,7 +7420,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7437,7 +7437,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7454,7 +7454,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7471,7 +7471,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7488,7 +7488,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7505,7 +7505,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7522,7 +7522,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7539,7 +7539,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7556,7 +7556,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7573,7 +7573,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7590,7 +7590,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7607,7 +7607,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7624,7 +7624,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7641,7 +7641,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7658,7 +7658,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7675,7 +7675,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7692,7 +7692,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7702,14 +7702,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7719,14 +7719,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7743,7 +7743,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7760,7 +7760,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7777,7 +7777,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7794,7 +7794,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7811,7 +7811,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7821,14 +7821,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7845,7 +7845,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7862,7 +7862,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7879,7 +7879,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7896,7 +7896,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7913,7 +7913,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7930,7 +7930,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7947,7 +7947,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7964,7 +7964,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7974,14 +7974,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7998,7 +7998,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8015,7 +8015,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8049,7 +8049,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8083,7 +8083,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8100,7 +8100,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8110,14 +8110,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8127,14 +8127,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8151,7 +8151,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8168,7 +8168,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8185,7 +8185,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8202,7 +8202,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8219,7 +8219,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8236,7 +8236,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8253,7 +8253,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8270,7 +8270,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8287,7 +8287,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8304,7 +8304,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8314,14 +8314,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8338,7 +8338,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8355,7 +8355,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8372,7 +8372,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8382,14 +8382,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8399,14 +8399,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8423,7 +8423,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8440,7 +8440,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8457,7 +8457,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8467,14 +8467,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8484,14 +8484,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8508,7 +8508,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8518,14 +8518,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8542,7 +8542,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8559,7 +8559,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8569,14 +8569,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8593,7 +8593,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8610,7 +8610,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -8620,14 +8620,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8644,7 +8644,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -8661,7 +8661,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -8678,7 +8678,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -8688,14 +8688,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -8712,7 +8712,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -8729,7 +8729,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -8739,14 +8739,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -8780,7 +8780,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -8824,14 +8824,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -8841,14 +8841,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8858,14 +8858,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8960,14 +8960,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -8977,14 +8977,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8994,14 +8994,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -9011,14 +9011,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -9035,7 +9035,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -9045,14 +9045,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -9062,14 +9062,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -9079,14 +9079,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -9103,7 +9103,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9171,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -9188,7 +9188,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9198,14 +9198,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -9215,14 +9215,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -9232,14 +9232,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -9256,7 +9256,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -9273,7 +9273,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -9283,14 +9283,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -9300,14 +9300,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -9317,14 +9317,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -9334,14 +9334,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -9358,7 +9358,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -9375,7 +9375,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -9385,14 +9385,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -9402,14 +9402,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -9419,14 +9419,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -9436,14 +9436,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9477,7 +9477,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -9487,14 +9487,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -9504,14 +9504,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9545,7 +9545,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9562,7 +9562,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -9572,14 +9572,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -9589,14 +9589,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -9613,7 +9613,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -9630,7 +9630,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -9647,7 +9647,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -9657,14 +9657,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -9674,14 +9674,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -9698,7 +9698,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -9708,14 +9708,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -9725,14 +9725,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -9749,7 +9749,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -9766,7 +9766,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -9776,14 +9776,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -9793,14 +9793,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -9810,14 +9810,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -9827,14 +9827,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -9851,7 +9851,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -9861,14 +9861,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -9885,7 +9885,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -9902,7 +9902,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9936,7 +9936,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -9953,7 +9953,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -10004,7 +10004,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -10014,14 +10014,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -10065,14 +10065,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -10089,7 +10089,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -10099,14 +10099,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -10116,14 +10116,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -10133,14 +10133,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -10150,14 +10150,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -10174,7 +10174,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -10184,14 +10184,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -10208,7 +10208,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -10218,14 +10218,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -10242,7 +10242,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -10252,14 +10252,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -10293,7 +10293,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -10327,7 +10327,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -10344,7 +10344,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -10354,14 +10354,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -10371,14 +10371,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -10395,7 +10395,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -10405,14 +10405,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -10429,7 +10429,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10446,7 +10446,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -10456,14 +10456,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -10480,7 +10480,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -10490,14 +10490,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -10514,7 +10514,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -10548,7 +10548,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -10582,7 +10582,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -10592,14 +10592,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -10616,7 +10616,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -10626,14 +10626,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -10650,7 +10650,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -10667,7 +10667,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -10677,14 +10677,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -10701,7 +10701,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -10718,7 +10718,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -10735,7 +10735,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -10745,14 +10745,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -10769,7 +10769,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -10786,7 +10786,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -10803,7 +10803,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -10820,7 +10820,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -10837,7 +10837,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -10854,7 +10854,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -10871,7 +10871,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -10888,7 +10888,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -10905,7 +10905,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -10922,7 +10922,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -10939,7 +10939,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -10956,7 +10956,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -10973,7 +10973,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -10990,7 +10990,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -11007,7 +11007,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -11075,7 +11075,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -11092,7 +11092,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -11109,7 +11109,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -11119,14 +11119,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -11136,14 +11136,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -11153,14 +11153,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -11177,7 +11177,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -11187,14 +11187,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -11211,7 +11211,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -11228,7 +11228,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -11245,7 +11245,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -11262,7 +11262,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -11279,7 +11279,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -11296,7 +11296,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -11313,7 +11313,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -11323,14 +11323,14 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -11340,14 +11340,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -11357,14 +11357,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -11374,14 +11374,14 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -11398,7 +11398,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -11408,14 +11408,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -11440,188 +11440,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HERA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0001250932</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>3.95199990272522</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>4.0485830956035</v>
-      </c>
-      <c r="I2" t="n">
-        <v>88</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PLC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005339160</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2.349999904632568</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>4.680851253787558</v>
-      </c>
-      <c r="I3" t="n">
-        <v>39</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Porto Aviation Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0005545238</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>10.10000038146973</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.8415841266298152</v>
-      </c>
-      <c r="I4" t="n">
-        <v>46</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11632,44 +11453,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/dividends_info_20260326.xlsx
+++ b/data/dividends_info_20260326.xlsx
@@ -7794,7 +7794,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7828,7 +7828,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7845,7 +7845,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7862,7 +7862,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7896,7 +7896,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7913,7 +7913,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7930,7 +7930,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7947,7 +7947,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7964,7 +7964,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -7998,7 +7998,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -8032,7 +8032,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8042,14 +8042,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8066,7 +8066,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8076,14 +8076,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8100,7 +8100,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8134,7 +8134,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8151,7 +8151,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8168,7 +8168,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8185,7 +8185,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8202,7 +8202,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8219,7 +8219,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8236,7 +8236,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8246,14 +8246,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8270,7 +8270,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8280,14 +8280,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8304,7 +8304,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8321,7 +8321,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8331,14 +8331,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8355,7 +8355,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8372,7 +8372,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8382,14 +8382,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8406,7 +8406,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8440,7 +8440,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8457,7 +8457,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8467,14 +8467,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8484,14 +8484,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8501,14 +8501,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8518,14 +8518,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8542,7 +8542,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8559,7 +8559,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8576,7 +8576,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8593,7 +8593,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -8627,7 +8627,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8661,7 +8661,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -8678,7 +8678,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -8695,7 +8695,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -8705,14 +8705,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -8729,7 +8729,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -8746,7 +8746,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -8780,7 +8780,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -8790,14 +8790,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8824,14 +8824,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8926,14 +8926,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -8960,14 +8960,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -8977,14 +8977,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8994,14 +8994,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -9011,14 +9011,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -9035,7 +9035,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -9045,14 +9045,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -9120,7 +9120,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9171,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -9188,7 +9188,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9198,14 +9198,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -9215,14 +9215,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -9232,14 +9232,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -9249,14 +9249,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -9266,14 +9266,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -9283,14 +9283,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -9307,7 +9307,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -9317,14 +9317,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -9341,7 +9341,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -9351,14 +9351,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -9402,14 +9402,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -9419,14 +9419,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -9436,14 +9436,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -9460,7 +9460,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -9477,7 +9477,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -9487,14 +9487,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -9511,7 +9511,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9521,14 +9521,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9538,14 +9538,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9562,7 +9562,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -9579,7 +9579,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -9589,14 +9589,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -9606,14 +9606,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -9630,7 +9630,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -9640,14 +9640,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -9664,7 +9664,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -9674,14 +9674,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -9691,14 +9691,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -9708,14 +9708,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -9725,14 +9725,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -9742,14 +9742,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -9793,14 +9793,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -9810,14 +9810,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -9827,14 +9827,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -9851,7 +9851,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -9861,14 +9861,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -9902,7 +9902,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -9919,7 +9919,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -9929,14 +9929,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -9953,7 +9953,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -9963,14 +9963,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -9980,14 +9980,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -9997,14 +9997,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -10014,14 +10014,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -10038,7 +10038,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -10055,7 +10055,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -10072,7 +10072,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -10082,14 +10082,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -10133,14 +10133,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -10157,7 +10157,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -10191,7 +10191,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -10208,7 +10208,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -10218,14 +10218,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -10242,7 +10242,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -10252,14 +10252,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -10269,14 +10269,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -10286,14 +10286,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -10310,7 +10310,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -10320,14 +10320,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -10344,7 +10344,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -10354,14 +10354,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -10371,14 +10371,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -10429,7 +10429,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10446,7 +10446,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -10463,7 +10463,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -10480,7 +10480,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -10497,7 +10497,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -10514,7 +10514,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -10541,14 +10541,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -10565,7 +10565,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -10582,7 +10582,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10616,7 +10616,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -10633,7 +10633,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -10650,7 +10650,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -10667,7 +10667,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -10684,7 +10684,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -10701,7 +10701,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -10718,7 +10718,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -10735,7 +10735,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -10745,14 +10745,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -10769,7 +10769,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -10786,7 +10786,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -10803,7 +10803,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -10820,7 +10820,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -10837,7 +10837,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -10854,7 +10854,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -10871,7 +10871,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -10888,7 +10888,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -10905,7 +10905,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -10922,7 +10922,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -10939,7 +10939,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -10956,7 +10956,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -10973,7 +10973,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -10990,7 +10990,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -11000,14 +11000,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -11024,7 +11024,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -11041,7 +11041,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -11058,7 +11058,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -11075,7 +11075,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -11092,7 +11092,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -11109,7 +11109,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -11177,7 +11177,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -11194,7 +11194,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -11211,7 +11211,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -11228,7 +11228,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -11238,14 +11238,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -11262,7 +11262,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -11272,14 +11272,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -11289,14 +11289,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -11313,7 +11313,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -11323,14 +11323,14 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -11340,14 +11340,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -11357,14 +11357,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -11374,14 +11374,14 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -11415,7 +11415,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
